--- a/cache/open_items_2026-05-13.xlsx
+++ b/cache/open_items_2026-05-13.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1016,315 +1016,243 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1 day + backtest</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>High win potential, medium risk</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+      <c r="N7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>KAIROS-MACRO-EVENTS</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>KAIROS-L2-BOOK</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1334,22 +1262,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1359,12 +1287,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1374,27 +1302,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="105" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1404,37 +1332,29 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1444,27 +1364,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1474,39 +1394,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1519,22 +1427,18 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1544,27 +1448,39 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1577,18 +1493,22 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1598,37 +1518,37 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1638,27 +1558,27 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1668,37 +1588,37 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1713,12 +1633,12 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1648,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1738,37 +1658,37 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1778,27 +1698,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1808,39 +1728,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>~12 min wall-clock</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1853,22 +1761,18 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="180" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1883,32 +1787,32 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1918,17 +1822,17 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1842,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1953,32 +1857,32 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -1988,27 +1892,27 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2018,37 +1922,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2063,22 +1967,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2088,37 +1992,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2128,27 +2032,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="180" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2158,37 +2062,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2198,27 +2102,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="105" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2228,29 +2132,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>30 min + backtest</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+        </is>
+      </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2265,22 +2177,22 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2290,22 +2202,22 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2315,12 +2227,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2335,22 +2247,22 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2360,37 +2272,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2400,27 +2312,27 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="75" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2430,27 +2342,39 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>shipped (revert candidate)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+        </is>
+      </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2458,23 +2382,27 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>fc76c9ec8</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="105" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2484,37 +2412,29 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>High — addresses #1 PF drag</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2529,12 +2449,12 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2464,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2554,22 +2474,22 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2579,12 +2499,12 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2599,22 +2519,22 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2624,37 +2544,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2664,17 +2584,17 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2604,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2694,22 +2614,22 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2727,58 +2647,58 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>0cdb13340</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr"/>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>VARIANT-F</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2788,67 +2708,67 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="105" customHeight="1">
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2858,67 +2778,67 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2928,69 +2848,57 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="75" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -3003,22 +2911,18 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -3028,37 +2932,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3068,27 +2972,27 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="105" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -3098,37 +3002,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3138,7 +3042,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3148,17 +3052,17 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -3168,37 +3072,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3213,22 +3117,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="90" customHeight="1">
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -3238,37 +3142,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3283,12 +3187,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3202,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -3308,37 +3212,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3348,17 +3252,17 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3272,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3378,37 +3282,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3418,27 +3322,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="90" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -3448,33 +3352,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
+          <t>10 min after answer</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Win: -158 lines + clearer docs.</t>
+        </is>
+      </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3489,22 +3397,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="75" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="90" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -3514,33 +3422,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>30 min after answers</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~3-5K lines if mostly stale.</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3555,22 +3467,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="135" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -3580,37 +3492,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3620,27 +3532,27 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -3650,37 +3562,37 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3695,22 +3607,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="90" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -3720,37 +3632,33 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Win: -50ms FCP.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3760,27 +3668,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="120" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="75" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -3790,37 +3698,33 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Win: -100ms FCP.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3835,12 +3739,12 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3754,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -3860,22 +3764,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3885,12 +3789,12 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3905,22 +3809,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="75" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -3930,29 +3834,37 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3962,27 +3874,27 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="105" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -3992,37 +3904,37 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4032,27 +3944,27 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="120" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -4062,22 +3974,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4087,12 +3999,12 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4107,22 +4019,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="105" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="135" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -4132,37 +4044,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4177,22 +4089,22 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -4202,37 +4114,29 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4242,27 +4146,27 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="120" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="105" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -4272,37 +4176,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4317,22 +4221,22 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="75" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -4342,37 +4246,37 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4382,27 +4286,27 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="105" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -4412,37 +4316,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
@@ -4452,27 +4356,27 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="75" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
@@ -4482,37 +4386,37 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4527,22 +4431,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="90" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="120" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -4552,37 +4456,37 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4597,22 +4501,22 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="90" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="75" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -4622,27 +4526,39 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+        </is>
+      </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4650,23 +4566,27 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr"/>
-    </row>
-    <row r="61" ht="105" customHeight="1">
+          <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -4676,29 +4596,37 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -4708,27 +4636,27 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="75" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -4738,37 +4666,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4726,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4808,37 +4736,37 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
@@ -4853,22 +4781,22 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="90" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -4878,22 +4806,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -4906,23 +4834,23 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>4442fa300</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="90" customHeight="1">
+    <row r="65" ht="105" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -4932,27 +4860,31 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4960,23 +4892,27 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66" ht="90" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -4986,27 +4922,39 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+        </is>
+      </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5014,23 +4962,27 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67" ht="75" customHeight="1">
+          <t>363984181</t>
+        </is>
+      </c>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="90" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -5040,27 +4992,39 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5068,7 +5032,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -5076,7 +5040,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="75" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -5084,7 +5052,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -5094,22 +5062,22 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -5122,23 +5090,23 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr"/>
     </row>
-    <row r="69" ht="60" customHeight="1">
+    <row r="69" ht="90" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -5148,39 +5116,27 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5188,27 +5144,23 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N69" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -5218,39 +5170,27 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5258,27 +5198,23 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
-        </is>
-      </c>
-      <c r="N70" s="8" t="inlineStr">
-        <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="105" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71" ht="75" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5288,31 +5224,27 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
-        </is>
-      </c>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5320,27 +5252,23 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
-        </is>
-      </c>
-      <c r="N71" s="8" t="inlineStr">
-        <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="105" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="75" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5350,31 +5278,27 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
-        </is>
-      </c>
+      <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5387,22 +5311,18 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
-        </is>
-      </c>
-      <c r="N72" s="8" t="inlineStr">
-        <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5412,37 +5332,37 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
@@ -5452,17 +5372,17 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5392,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5482,35 +5402,39 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr"/>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Trivial.</t>
+        </is>
+      </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5518,17 +5442,17 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5462,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5548,37 +5472,29 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>1.5 hrs</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
@@ -5593,60 +5509,56 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="105" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-B</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr"/>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+        </is>
+      </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5654,67 +5566,67 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="75" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-2</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
+          <t>Low risk / Medium win (consistency)</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
@@ -5724,56 +5636,64 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="75" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RULE-1</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="5" t="inlineStr"/>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
       <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="12" t="inlineStr">
         <is>
@@ -5787,56 +5707,64 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N78" s="8" t="inlineStr"/>
-    </row>
-    <row r="79" ht="45" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N78" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="105" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5844,27 +5772,27 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="45" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -5874,39 +5802,35 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr"/>
       <c r="K80" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5914,17 +5838,17 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5858,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -5944,22 +5868,22 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5969,12 +5893,12 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -5989,22 +5913,22 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="60" customHeight="1">
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -6014,39 +5938,27 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
       <c r="K82" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6059,22 +5971,18 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N82" s="8" t="inlineStr">
-        <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="60" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83" ht="45" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -6084,39 +5992,35 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6124,27 +6028,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -6154,37 +6058,37 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -6199,22 +6103,22 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="75" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -6224,37 +6128,37 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K85" s="12" t="inlineStr">
@@ -6269,22 +6173,22 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="150" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -6294,29 +6198,37 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
+        </is>
+      </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -6331,22 +6243,22 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="120" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -6356,37 +6268,37 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs + backtest validation</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Medium — changes live size or eliminates a layer</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K87" s="12" t="inlineStr">
@@ -6396,27 +6308,27 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="75" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -6426,27 +6338,39 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6454,23 +6378,27 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr"/>
-    </row>
-    <row r="89" ht="105" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -6480,29 +6408,37 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
@@ -6512,27 +6448,27 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N89" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="135" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="150" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -6542,37 +6478,29 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
@@ -6587,22 +6515,22 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="120" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -6612,31 +6540,27 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6644,19 +6568,15 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N91" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr"/>
     </row>
     <row r="92" ht="45" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -6664,49 +6584,37 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-10</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="5" t="inlineStr"/>
       <c r="K92" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6714,15 +6622,15 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N92" s="8" t="inlineStr"/>
     </row>
     <row r="93" ht="45" customHeight="1">
       <c r="A93" s="2" t="n">
@@ -6730,49 +6638,37 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-11</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>verified (no change needed)</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
-        </is>
-      </c>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="5" t="inlineStr"/>
       <c r="K93" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6780,15 +6676,15 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr">
-        <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr"/>
     </row>
     <row r="94" ht="45" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -6796,44 +6692,36 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SHARPE-12</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr"/>
       <c r="K94" s="12" t="inlineStr">
         <is>
@@ -6842,19 +6730,15 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
-      <c r="N94" s="8" t="inlineStr">
-        <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
-        </is>
-      </c>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N94" s="8" t="inlineStr"/>
     </row>
     <row r="95" ht="45" customHeight="1">
       <c r="A95" s="2" t="n">
@@ -6862,7 +6746,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
@@ -6872,51 +6756,43 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>5 min after answer</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K95" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="3" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr">
-        <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr"/>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="inlineStr"/>
     </row>
     <row r="96" ht="45" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -6924,7 +6800,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -6934,51 +6810,43 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>hours-days each</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K96" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="3" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr">
-        <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="inlineStr"/>
     </row>
     <row r="97" ht="45" customHeight="1">
       <c r="A97" s="2" t="n">
@@ -6986,257 +6854,1221 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>SHARPE-4</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
-        <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K97" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="3" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr">
-        <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="75" customHeight="1">
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98" ht="45" customHeight="1">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>SHARPE-5</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>2-3 hrs</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>Win: catches accidental layout regressions.</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
-        </is>
-      </c>
-      <c r="K98" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="5" t="inlineStr"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr">
-        <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="195" customHeight="1">
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99" ht="45" customHeight="1">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
+          <t>SHARPE-6</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Sharpe Roadmap</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Portfolio Sharpe KPI vs target</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Annualized Sharpe target tracking + gap report</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr"/>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100" ht="45" customHeight="1">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>SHARPE-7</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Sharpe Roadmap</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Sharpe-based stop sizing</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101" ht="45" customHeight="1">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>SHARPE-8</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Sharpe Roadmap</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Sortino computation alongside Sharpe</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Downside-only vol denominator added everywhere</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr"/>
+      <c r="J101" s="5" t="inlineStr"/>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N101" s="8" t="inlineStr"/>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>SHARPE-9</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Sharpe Roadmap</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>SPY-Sharpe regime cross-validation</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr"/>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N102" s="8" t="inlineStr"/>
+    </row>
+    <row r="103" ht="120" customHeight="1">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>CONVICTION-TIER-WIRE</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Strategy / Conviction</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Conviction tier: simplified to score-band only</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N103" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="75" customHeight="1">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>ENTRY-Q-AB</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Strategy / Gates</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Regime-conditional entry_quality A/B</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="5" t="inlineStr"/>
+      <c r="J104" s="5" t="inlineStr"/>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>07c3af6a3</t>
+        </is>
+      </c>
+      <c r="N104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105" ht="105" customHeight="1">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>TRACKER-BUY-FILTER</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Tracker/Feedback Loop</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+        </is>
+      </c>
+      <c r="K105" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N105" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="135" customHeight="1">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Scanner deep refactor</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N106" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="120" customHeight="1">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Validation Hygiene</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N107" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="45" customHeight="1">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Verify backtest persistence (cb1f5a010)</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr"/>
+      <c r="N108" s="8" t="inlineStr">
+        <is>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="45" customHeight="1">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>verified (no change needed)</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr"/>
+      <c r="N109" s="8" t="inlineStr">
+        <is>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="45" customHeight="1">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C110" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Remove emoji icons from Thesis + Research labels</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr"/>
+      <c r="K110" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
+      <c r="N110" s="8" t="inlineStr">
+        <is>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="45" customHeight="1">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Code Cleanup (DEFERRED)</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>5 min after answer</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
+      <c r="N111" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="45" customHeight="1">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K112" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="3" t="inlineStr"/>
+      <c r="N112" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="45" customHeight="1">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr"/>
+      <c r="N113" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="75" customHeight="1">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K114" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr"/>
+      <c r="N114" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="195" customHeight="1">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F115" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I115" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K99" s="15" t="inlineStr">
+      <c r="K115" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="M99" s="3" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr">
+      <c r="M115" s="3" t="inlineStr"/>
+      <c r="N115" s="8" t="inlineStr">
         <is>
           <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="90" customHeight="1">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
+    <row r="116" ht="90" customHeight="1">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Data / Universe</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>Russell 1000 historical membership (Sharadar SF1)</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
         <is>
           <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>$$ + 1 day</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I116" s="5" t="inlineStr">
         <is>
           <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="J116" s="5" t="inlineStr">
         <is>
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K100" s="15" t="inlineStr">
+      <c r="K116" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="M100" s="3" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr">
+      <c r="M116" s="3" t="inlineStr"/>
+      <c r="N116" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -7303,10 +8135,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -7341,10 +8173,10 @@
         <v>43</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -7398,10 +8230,10 @@
         <v>47</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
